--- a/교육용_대전게임_문제데이터_v2.xlsx
+++ b/교육용_대전게임_문제데이터_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10450" yWindow="2540" windowWidth="15150" windowHeight="11170" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분량" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="난이도" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="주제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="분량" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="난이도" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="22.5" customWidth="1" min="3" max="3"/>
@@ -479,7 +479,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>쉬움</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>어려움</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>어려움</t>
+          <t>매우 어려움</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2260,6 +2260,606 @@
       <c r="F61" t="inlineStr">
         <is>
           <t>ethology,imprinting,instinct,social behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>사과</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>과일,씨앗,껍질</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>apple,fruit,seed,peel</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>바나나</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>노란색,원숭이,열대</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>banana,yellow,monkey,tropical</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>눈사람</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>눈덩이,겨울,당근</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>snowman,snowball,winter,carrot</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>태양</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한낮,햇살,더위</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>sun,noon,sunshine,heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>개구리</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>올챙이,연못,점프</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>frog,tadpole,pond,jump</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>토끼</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>깡충깡충,긴귀,풀밭</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>rabbit,long ears,grass field</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>비누</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>거품,세균,깨끗</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>soap,bubble,germ,clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>시계</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>시침,분침,숫자</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>clock,hour hand,minute hand,number</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>칫솔</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>치약,양치,충치</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>toothbrush,toothpaste,brushing,cavity</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>연필</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>지우개,흑연,공책</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>pencil,eraser,graphite,notebook</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>오리</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>부리,깃털,헤엄</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>duck,beak,feather,swim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>사자</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>갈기,포효,초원</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>lion,mane,roar,savanna</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>코끼리</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>상아,아프리카,몸집</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>elephant,tusk,africa,body size</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>식빵</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>밀가루,오븐,토스트</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>bread,flour,oven,toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>달걀</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>노른자,흰자,껍데기</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>egg,yolk,egg white,shell,계란</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>수박</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>여름,줄무늬,초록색</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>watermelon,summer,stripes,green</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>신호등</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>빨간불,초록불,횡단보도</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>traffic light,red light,green light,crosswalk</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>별자리</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>밤하늘,북두칠성,반짝</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>constellation,night sky,big dipper,twinkle,성좌</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>자동차</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>운전,핸들,도로</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>car,driving,steering wheel,road,차량</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>수영</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>물안경,배영,풀장</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>swimming,goggles,backstroke,pool</t>
         </is>
       </c>
     </row>
@@ -2425,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="3" max="3"/>
@@ -2449,45 +3049,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>쉬움</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>정말 쉬운 일상 주제. 필수어 3개 중 1개 이상 답변에 있으면 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>필수어 3개 중 1개 이상 답변에 있으면 통과</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>필수어 3개 중 2개 이상 답변에 있으면 통과</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>어려움</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>필수어 3개 모두 답변에 있어야 통과</t>
         </is>

--- a/교육용_대전게임_문제데이터_v2.xlsx
+++ b/교육용_대전게임_문제데이터_v2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="22.5" customWidth="1" min="3" max="3"/>
@@ -2860,6 +2860,9606 @@
       <c r="F81" t="inlineStr">
         <is>
           <t>swimming,goggles,backstroke,pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>딸기</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>빨간색,새콤달콤,씨앗겉</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>strawberry,red,sweet and sour,seeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>포도</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>송이,보라색,와인</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>grape,bunch,purple,wine</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>오렌지</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>주황색,비타민,과즙</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>orange,orange color,vitamin,juice</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>감자</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>땅속,튀김,수확</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>potato,underground,fries,harvest</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>토끼,뿌리채소,주황빛</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>carrot,rabbit,root vegetable,orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>옥수수</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>알갱이,팝콘열매,수확철</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>corn,kernel,popcorn,harvest</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>호박</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>넝쿨,할로윈,주황빛깔</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>pumpkin,vine,halloween,orange hue</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>라면</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>면발,스프,끓는물</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ramen,noodles,soup powder,boiling water</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>햄버거</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>패티,동그란빵,케첩</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>hamburger,patty,round bun,ketchup</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>샌드위치</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>속재료,양상추,도시락</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>sandwich,filling,lettuce,lunch box</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>주스</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>믹서,유리컵,빨대</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>juice,blender,glass,straw</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>초콜릿</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>카카오,달콤한,발렌타인</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>chocolate,cacao,sweet,valentine</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>사탕</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>설탕,입안,알록달록</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>candy,sugar,mouth,colorful</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>쿠키</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>바삭바삭,초코칩,간식</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>cookie,crispy,chocolate chip,snack</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>케이크</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>생일,촛불,생크림</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>cake,birthday,candle,whipped cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>김밥</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>단무지,소풍도시락,김발</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>gimbap,pickled radish,picnic lunch,bamboo mat</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>떡볶이</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>고추장,어묵,분식</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>tteokbokki,red pepper paste,fish cake,snack food</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>고구마</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>군것질,겨울간식,보랏빛</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>sweet potato,snack,winter snack,purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>수프</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>국물,숟가락,따뜻한</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>soup,broth,spoon,warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>팝콘</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>영화관,튀기다,버터</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>popcorn,cinema,pop,butter</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>두부</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>콩물,부드러운,말랑말랑</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>tofu,soy milk,tender,soft</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>펭귄</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>남극,뒤뚱뒤뚱,빙하</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>penguin,antarctica,waddle,glacier</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>기린</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>긴목,아카시아,얼룩무늬</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>giraffe,long neck,acacia,spotted</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>호랑이</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>맹수,백두산,어흥</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>tiger,fierce beast,baekdu,roar</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>북극곰</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>얼음땅,하얀털,물범</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>polar bear,ice land,white fur,seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>침팬지</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>영장류,도구사용,바나나껍질</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>chimpanzee,primate,tool use,banana peel</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>돌고래</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>초음파,지능,수족관</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>dolphin,ultrasound,intelligence,aquarium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>고래</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>거대한,물줄기,포유류</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>whale,huge,spout,mammal</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>상어</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>지느러미,날카로운이빨,사냥꾼</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>shark,fin,sharp teeth,hunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>거북이</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>등껍질,느림보,장수</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>turtle,shell,slowpoke,longevity</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>다람쥐</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>도토리,볼주머니,겨울잠</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>squirrel,acorn,cheek pouch,hibernation</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>꿀벌</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>벌집,꽃가루,여왕벌</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>honeybee,hive,pollen,queen bee</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>개미</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>여왕,행렬,부지런함</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ant,queen,line,diligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>잠자리</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>겹눈,투명한날개,가을하늘</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>dragonfly,compound eye,transparent wings,autumn sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>거미</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>줄치기,여덟개,먹잇감</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>spider,spinning,eight,prey</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>참새</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>짹짹,전깃줄,낟알</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>sparrow,chirp,wire,grain</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>독수리</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>맹금류,부리와발톱,활강</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>eagle,bird of prey,beak and claws,glide</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>부엉이</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>올빼미,야간,커다란눈</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>owl,owlet,night,big eyes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>앵무새</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>흉내,알록달록한깃,말하는새</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>parrot,mimic,colorful feathers,talking bird</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>낙타</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>쌍봉,오아시스,물저장</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>camel,two humps,oasis,water storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>판다</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>대나무,중국,흑백</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>panda,bamboo,china,black and white</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>가방</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>어깨끈,지퍼,등교</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>bag,strap,zipper,going to school</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>신발</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>운동화,매듭,발바닥</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>shoes,sneakers,knot,sole</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>모자</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>챙넓은,머리,햇볕가리개</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>hat,wide brim,head,sun shade</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>안경</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>렌즈,콧등,시력</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>glasses,lens,nose,eyesight</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>양말</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>발목,뜨개질,겨울발</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>socks,ankle,knitting,winter feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>장갑</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>손가락,털실,추위</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>gloves,fingers,yarn,cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>거울</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>반사,얼굴,화장대</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>mirror,reflection,face,dressing table</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>냉장고</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>냉동실,반찬통,시원한</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>refrigerator,freezer,side dish container,cool</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>세탁기</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>빨래,세제,탈수</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>washing machine,laundry,detergent,spin dry</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>전화기</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>통화,벨소리,전화번호</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>telephone,call,ringtone,phone number</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>침대</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>매트리스,베개,숙면</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>bed,mattress,pillow,deep sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>책상</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>서랍,공부,스탠드</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>desk,drawer,study,desk lamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>의자</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>등받이,다리넷,앉다</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>chair,backrest,four legs,sit</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>열쇠</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>자물쇠구멍,키링,현관문</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>key,keyhole,key ring,front door</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>가위</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>손잡이날,종이자르기,싹둑</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>scissors,handle blade,cutting paper,snip</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>풍선</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>헬륨,터지다,생일파티</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>balloon,helium,burst,birthday party</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>인형</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>곰돌이,장난감,포근한</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>doll,teddy bear,toy,cuddly</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>크레파스</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>그림,색칠,스케치북</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>crayon,drawing,coloring,sketchbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>달력</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>날짜,요일,열두달</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>calendar,date,day of week,twelve months</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>선풍기</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>날개바람,더운여름,회전</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>fan,blades wind,hot summer,rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>텔레비전</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>리모컨,채널,방송</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>television,remote control,channel,broadcast</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>전구</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>필라멘트,스위치,불빛</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>light bulb,filament,switch,light</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>번개</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>천둥,번쩍,소나기구름</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>lightning,thunder,flash,rain cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>구름</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>하늘높이,뭉게뭉게,솜사탕</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>cloud,high in the sky,fluffy,cotton candy</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>바람</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>선선한,날리다,방향</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>wind,cool breeze,blow,direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>안개</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>뿌옇다,아침,시야</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>fog,hazy,morning,visibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>풀잎,새벽,물방울</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>dew,grass blade,dawn,water drop</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>폭포</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>낙차,물보라,절벽</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>waterfall,drop,spray,cliff</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>호수</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>잔잔한,배타기,물가</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>lake,calm,boating,waterside</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>사막</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>모래언덕,선인장,뜨거운</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>desert,sand dune,cactus,hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>단풍</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>가을산,붉게물들다,낙엽</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>maple leaves,autumn mountain,turn red,fallen leaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>눈송이</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>육각형,겨울하늘,녹다</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>snowflake,hexagon,winter sky,melt</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>파도</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>해변,물결,서핑</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>wave,beach,ripple,surfing</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>모래</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>성쌓기,바닷가,알갱이들</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>sand,castle,seaside,grains</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>갯벌</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>조개,썰물,진흙</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>tidal flat,clam,low tide,mud</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>반딧불</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>깜깜한밤,빛나는,여름밤</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>firefly,dark night,glowing,summer night</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>화분</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>흙덩이,물주기,베란다</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>flowerpot,soil,watering,veranda</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>젓가락</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>한쌍,밥상,집게질</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>chopsticks,pair,dining table,pinching</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>숟가락</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>떠먹기,밥상차림,스푼</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>쉬움</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>spoon,scooping,table setting,tablespoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>비빔밥</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>나물,고명,참기름</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>bibimbap,namul,garnish,sesame oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>삼겹살</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>불판,쌈채소,회식</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>pork belly,grill,lettuce wrap,company dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>만두</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>소고기,빚기,찜기</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>dumpling,beef,wrapping,steamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>원두,카페인,에스프레소</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>coffee,beans,caffeine,espresso</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>치킨</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>튀김옷,배달,양념</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>chicken,batter,delivery,seasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>냉면</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>메밀,육수,얼음</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>cold noodles,buckwheat,broth,ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>팥빙수</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>단팥,연유,얼음갈이</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>patbingsu,sweet red bean,condensed milk,shaved ice</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>토스트</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>바삭,토스터,아침식사</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>toast,crispy,toaster,breakfast</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>원숭이</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>꼬리감기,나무타기,영리함</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>monkey,tail grip,tree climbing,clever</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>캠핑</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>텐트,모닥불,별구경</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>camping,tent,campfire,stargazing</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>놀이공원</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>롤러코스터,줄서기,회전목마</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>amusement park,roller coaster,queueing,carousel</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>영화관</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>팝콘,스크린,상영관</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>cinema,popcorn,screen,theater</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>학교</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>교실,선생님,종소리</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>school,classroom,teacher,bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>병원</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>의사,진료,처방</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>hospital,doctor,treatment,prescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>공항</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>비행기표,탑승구,수하물</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>airport,flight ticket,boarding gate,baggage</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>지하철</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>환승,개찰구,승강장</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>subway,transfer,ticket gate,platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>튜브,물놀이,구명조끼</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>swimming pool,tube,water play,life jacket</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>소풍</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>돗자리,도시락소리,봄나들이</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>picnic,mat,lunchbox,spring outing</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>생일</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>축하,선물꾸러미,미역국</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>birthday,congratulation,gifts,seaweed soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>포장,트럭,새집</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>moving,packing,truck,new house</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>택배</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>송장,배송,현관앞</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>parcel,invoice,shipping,doorstep</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>청소</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>빗자루,걸레,먼지털기</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>cleaning,broom,mop,dusting</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>빨래</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>건조대,빨랫줄,섬유유연제</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>laundry,drying rack,clothesline,fabric softener</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>설거지</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>수세미,그릇,고무장갑</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>dishwashing,scrubber,dishes,rubber gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>운동회</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>달리기,줄다리기,청팀백팀</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>sports day,running,tug of war,blue and white team</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>방학</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>겨울나기,숙제,늦잠</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>vacation,wintering,homework,sleeping in</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>우체국</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>편지,소포,우표</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>post office,letter,package,stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>편의점</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>삼각김밥,야간영업,계산대</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>convenience store,triangle gimbap,late night,checkout</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>태풍</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>강풍,휴교,열대저기압</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>typhoon,strong wind,school closure,tropical cyclone</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>일식</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>달그림자,금환,개기</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>solar eclipse,moon shadow,ring of fire,total</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>화성</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>붉은행성,탐사선,사막행성</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>mars,red planet,rover,desert planet</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>밀물</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>해수면,만조,바닷물</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>high tide,sea level,flood tide,seawater</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>온천</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>화산열,유황,노천탕</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>hot spring,volcanic heat,sulfur,open-air bath</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>자석</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>N극,끌어당김,나침반</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>magnet,north pole,attraction,compass</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>얼음</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>고체,영하,녹는점</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ice,solid,below zero,melting point</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>소금</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>짠맛,염전,결정알</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>salt,salty,salt farm,crystal grains</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>그림자</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>빛가림,길어짐,해시계</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>shadow,blocking light,lengthening,sundial</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>메아리</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>높은산,울림,되돌아오는소리</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>echo,high mountain,reverberation,returning sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>씨앗</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>싹틔우기,발아,열매속</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>seed,sprouting,germination,inside fruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>곰팡이</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>습기,푸른빛,식빵위</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>mold,humidity,bluish,on bread</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>올림픽</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>금메달,성화,오륜기</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>olympics,gold medal,torch,five rings</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>피아노</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>건반,페달밟기,악보</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>piano,keys,pedaling,sheet music</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>여섯줄,연주,코드잡기</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>guitar,six strings,playing,fingering chords</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>발레</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>토슈즈,백조,우아함</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ballet,toe shoes,swan,grace</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>만화</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>칸나누기,말풍선,웹툰</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>comics,panels,speech bubble,webtoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>동화</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>옛날옛적,교훈,공주</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>fairy tale,once upon a time,moral,princess</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>박물관</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>유물,전시,관람</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>museum,relic,exhibition,visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>한복</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>저고리,치마,명절</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>hanbok,jeogori,skirt,holiday</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>태권도</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>품새,겨루기,검은띠</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>taekwondo,poomsae,sparring,black belt</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>스마트폰</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>터치,애플리케이션,문자메시지</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>smartphone,touch,application,text message</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>센서,프로그램,자동화</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>robot,sensor,program,automation</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>게임</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>레벨,캐릭터조작,승패</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>game,level,character control,win or lose</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>유튜브</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>구독,영상,알고리즘추천</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>youtube,subscribe,video,recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>용돈</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>지폐,동전,저금통</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>allowance,money,banknote,coin,piggy bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>경찰</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>순찰,신고,112</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>police,patrol,report,emergency number</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>소방관</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>화재,사다리차,119</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>firefighter,fire,ladder truck,fire number</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>짜장면</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>춘장,배달음식,젓가락비비기</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>jajangmyeon,black bean sauce,delivery food,mixing with chopsticks</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>된장찌개</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>메주,구수,뚝배기</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>doenjang stew,fermented soybean,savory,earthen pot</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>불고기</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>양념고기,달짝지근,석쇠</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>bulgogi,marinated meat,sweet and savory,grill</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>스파게티</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>토마토소스,포크돌리기,이탈리아</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>spaghetti,tomato sauce,fork twirling,italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>도넛</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>구멍,튀김반죽,설탕코팅</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>donut,hole,fried dough,sugar glaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>핫도그</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>소시지,막대,케첩머스타드</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>hot dog,sausage,stick,ketchup mustard</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>꽃게</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>집게발,옆걸음,간장게장</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>crab,pincers,sideways walking,soy sauce crab</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>오징어</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>먹물,열개다리,건조</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>squid,ink,ten arms,dried</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>까치</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>설날,길조,까악</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>magpie,lunar new year,good omen,caw</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>여우</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>꾀많은,구미호,붉은털</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>fox,cunning,nine-tailed,red fur</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>사슴</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>녹용,초식,산속</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>deer,antlers,herbivore,deep mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>박쥐</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>동굴,초음파탐지,거꾸로</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>bat,cave,echolocation,upside down</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>달팽이</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>나선껍질,더듬이,느릿느릿</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>동물</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>snail,spiral shell,antennae,slowly</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>엘리베이터</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>층수버튼,승강기,고층</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>elevator,floor button,lift,high-rise</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>횡단보도</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>초록신호,건널목,흰선</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>crosswalk,green signal,crossing,white lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>우산</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>빗물,접이식,장대비</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>umbrella,rainwater,folding,downpour</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>식당</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>메뉴판,주문,종업원</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>restaurant,menu,order,waiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>파마,가위질,염색</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>hair salon,perm,cutting,dyeing</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>세차</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>물총,왁스,광택</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>car wash,water gun,wax,polish</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>요리</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>레시피,불조절,재료손질</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>cooking,recipe,heat control,prepping ingredients</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>산책로</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>벤치,가로수,운동복</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>walking trail,bench,street trees,sportswear</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>눈썰매</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>언덕,스키장,겨울놀이</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>sledding,hill,ski resort,winter play</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>등산</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>정상,배낭,산행</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>생활</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>hiking,summit,backpack,mountain trek</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>무지개떡</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>오색,찜기떡,잔치음식</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>rainbow rice cake,five colors,steamed cake,feast food</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>중력</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>질량,낙하,뉴턴</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>gravity,mass,falling,newton</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>마찰력</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>접촉면,미끄러짐,브레이크</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>friction,contact surface,slipping,brake</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>부력</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>아르키메데스,뜨는힘,선박</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>buoyancy,archimedes,floating force,vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>빛의반사</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>입사각,반사각,법선</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>reflection of light,incident angle,reflection angle,normal line</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>소리의전달</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>떨림,매질,음파</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>sound transmission,tremor,medium,sound wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>자기장</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>자기력선,전자석,코일</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>magnetic field,field lines,electromagnet,coil</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>산화</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>녹슨,산소결합,쇠붙이</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>oxidation,rusted,oxygen bonding,metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>연소</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>발화점,탄소,불꽃</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>combustion,ignition point,carbon,flame</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>산성비</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>이산화황,산성도,부식</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>acid rain,sulfur dioxide,acidity,corrosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>온실효과</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>이산화탄소층,복사열,지구온난화</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>greenhouse effect,carbon dioxide layer,radiant heat,global warming</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>물의순환</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>응결,강수,지하수</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>water cycle,condensation,precipitation,groundwater</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>암석</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>화성암,퇴적암,변성암</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>rock,igneous,sedimentary,metamorphic</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>화석</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>퇴적층,고생물,지질시대</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>fossil,sediment layer,paleontology,geological age</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>달의위상</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>삭망,초승달,상현</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>phases of the moon,new and full moon,crescent,first quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>계절</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>공전,자전축,기울기</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>season,revolution,rotation axis,tilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>은하수</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>성단,나선팔,수많은별</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>milky way,star cluster,spiral arm,countless stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>혈액순환</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>심장박동,동맥,정맥</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>blood circulation,heartbeat,artery,vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>호흡기관</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>허파,기관지,가스교환</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>respiratory organ,lungs,bronchi,gas exchange</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>뼈와근육</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>관절,골격,수축이완</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>bones and muscles,joint,skeleton,contraction and relaxation</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>감각기관</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>망막,고막,신경전달</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>sense organs,retina,eardrum,nerve transmission</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>식물의한살이</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>떡잎,개화,결실</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>plant life cycle,cotyledon,flowering,fruiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>곤충</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>가슴,세쌍다리,탈피</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>insect,thorax,three pairs of legs,molting</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>세포분열</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>염색체,복제,체세포</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>cell division,chromosome,replication,somatic cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>멸종위기종</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>서식지파괴,보호구역,복원사업</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>endangered species,habitat loss,reserve,restoration project</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>먹이그물</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>포식자,피식자,에너지흐름</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>food web,predator,prey,energy flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>탄소순환</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>화석연료,흡수원,배출</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>carbon cycle,fossil fuel,sink,emission</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>태양광발전</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>집광판,신재생,햇빛에너지</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>solar power,solar panel,renewable,sunlight energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>원자력발전</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>우라늄,핵분열,방사능</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>nuclear power,uranium,fission,radiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>퇴적</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>침식작용,삼각주,운반</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>deposition,erosion,delta,transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>조류</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>난류,한류,해수흐름</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ocean current,warm current,cold current,seawater flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>용해</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>용질,용매,포화</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>dissolution,solute,solvent,saturation</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>혼합물</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>분리,거름종이,증류</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>mixture,separation,filter paper,distillation</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>삼국시대</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>고구려,백제,신라</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>three kingdoms,goguryeo,baekje,silla</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>임진왜란</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>이순신,거북선,의병</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>imjin war,yi sun-sin,turtle ship,righteous army</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>세종대왕</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>집현전,측우기,애민정신</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>king sejong,hall of worthies,rain gauge,love for people</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>독립운동</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>삼일운동,임시정부,유관순</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>independence movement,march first movement,provisional government,yu gwan-sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>광복</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>해방,1945년,태극기</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>liberation,emancipation,1945,taegukgi</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>고조선</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>단군,8조법,청동기</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>gojoseon,dangun,eight laws,bronze age</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>발해</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>대조영,해동성국,옛고구려땅</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>balhae,dae jo-yeong,prosperous land of the east,former goguryeo land</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>대동여지도</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>김정호,목판,정밀지도</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>daedongyeojido,kim jeong-ho,woodblock,precise map</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>거북선</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>철갑,돌격선,용머리</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>turtle ship,ironclad,assault ship,dragon head</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>훈민정음</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>창제,반포,백성글</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>hunminjeongeum,creation,proclamation,people's script</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>고인돌</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>거석,무덤돌,선사시대</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>dolmen,megalith,tomb stone,prehistoric</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>프랑스혁명</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>바스티유,인권선언,왕정몰락</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>french revolution,bastille,declaration of rights,fall of monarchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>로마제국</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>콜로세움,황제,속주</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>roman empire,colosseum,emperor,province</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>대항해시대</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>신항로,콜럼버스,식민지개척</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>age of discovery,new sea route,columbus,colonization</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>삼권분립</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>입법부,행정부,사법부</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>separation of powers,legislature,executive,judiciary</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>선거</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>투표,후보,유권자</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>election,voting,candidate,voter</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>헌법</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>기본권,국민주권,최고법</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>constitution,fundamental rights,popular sovereignty,supreme law</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>국회</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>법률제정,의원,본회의</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>national assembly,lawmaking,lawmaker,plenary session</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>세금</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>납세,소득세,국가재정</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>tax,tax payment,income tax,national finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>물가</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>인플레이션,소비자,화폐가치</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>prices,inflation,consumer,currency value</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>수출입</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>관세,무역수지,항구</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>import and export,tariff,trade balance,port</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>저출산</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>육아,출산율하락,인구절벽</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>low birth rate,childcare,declining fertility,demographic cliff</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>다문화</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>이주민,공존,문화다양성</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>multiculture,immigrant,coexistence,cultural diversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>환경오염</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>미세플라스틱,폐수,분리배출</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>environmental pollution,microplastics,wastewater,recycling sorting</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>재난안전</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>대피요령,지진대비,안전교육</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>disaster safety,evacuation guide,earthquake preparedness,safety education</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>인권</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>평등,존엄성,차별금지</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>human rights,equality,dignity,anti-discrimination</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>지방자치</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>시장,조례,주민참여</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>local autonomy,mayor,ordinance,resident participation</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>신문</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>사설,기자,기사</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>newspaper,editorial,reporter,article</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>알고리즘</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>순서도,절차,반복문</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>algorithm,flowchart,procedure,loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>변수,함수,디버깅</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>coding,variable,function,debugging</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>암호화</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>복호화,열쇠값,보안통신</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>encryption,decryption,key value,secure communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>클라우드</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>원격저장,서버농장,구독형</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>cloud,remote storage,server farm,subscription</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>빅데이터</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>대량정보,분석,통계패턴</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>big data,mass information,analysis,statistical pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>가상현실</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>헤드셋,몰입,3D공간</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>virtual reality,headset,immersion,3d space</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>사물인터넷</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>스마트홈,센서연결,원격제어</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>internet of things,smart home,sensor connection,remote control</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>개인정보</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>유출,동의서,비밀번호</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>personal information,leak,consent form,password</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>저작권</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>창작자,무단복제,표절</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>copyright,creator,unauthorized copying,plagiarism</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>해킹</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>침입,바이러스,방화벽</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>hacking,intrusion,virus,firewall</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>고전문학</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>춘향전,홍길동전,옛이야기</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>classical literature,chunhyangjeon,honggildongjeon,old tales</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>수필</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>체험,고백적글,자유형식</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>essay,experience,confessional writing,free form</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>국악</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>가야금,장구,풍류</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>gugak,gayageum,janggu,elegance</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>오케스트라</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>지휘자,현악기,교향곡</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>orchestra,conductor,string instruments,symphony</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>뮤지컬</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>넘버,무대,배우</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>musical,number,stage,actor</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>탈춤</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>하회탈,풍자,마당극</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>talchum,hahoe mask,satire,madang play</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>수묵화</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>먹빛,여백,화선지</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ink painting,ink color,blank space,rice paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>건축</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>설계도,기둥,서까래</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>architecture,blueprint,pillar,rafter</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>영화제작</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>감독,촬영팀,편집</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>filmmaking,director,camera crew,editing</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>한국전쟁</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>휴전,삼팔선,피난</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>어려움</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>korean war,armistice,38th parallel,evacuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>열역학</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>엔트로피,열기관,에너지보존</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>thermodynamics,entropy,heat engine,energy conservation</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>전자기유도</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>패러데이,자속변화,유도전류</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>electromagnetic induction,faraday,flux change,induced current</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>도플러효과</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>파장변화,적색편이,구급차소리</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>doppler effect,wavelength shift,redshift,ambulance sound</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>블랙홀</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>사건의지평선,특이점,슈바르츠실트</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>black hole,event horizon,singularity,schwarzschild</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>빅뱅이론</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>우주팽창,배경복사,초기우주</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>big bang theory,cosmic expansion,background radiation,early universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>핵융합</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>플라즈마,중수소,토카막</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>nuclear fusion,plasma,deuterium,tokamak</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>실리콘,도핑,트랜지스터</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>semiconductor,silicon,doping,transistor</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>초전도체</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>임계온도,저항없음,마이스너</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>superconductor,critical temperature,zero resistance,meissner</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>화학평형</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>르샤틀리에,역반응,평형상수</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>chemical equilibrium,le chatelier,reverse reaction,equilibrium constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>산화환원</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>전자이동,산화수,환원제</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>redox,electron transfer,oxidation number,reducing agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>촉매</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>활성화에너지,반응속도,효소유사</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>catalyst,activation energy,reaction rate,enzyme-like</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>유기화학</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>탄화수소,작용기,이성질체</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>organic chemistry,hydrocarbon,functional group,isomer</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>엔탈피</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>반응열,발열반응,흡열반응</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>enthalpy,heat of reaction,exothermic,endothermic</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>DNA복제</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>이중나선,중합효소,반보존적</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>dna replication,double helix,polymerase,semiconservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>단백질합성</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>전사,번역,리보솜</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>protein synthesis,transcription,translation,ribosome</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>유전자편집</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>크리스퍼,가위효소,염기서열</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>gene editing,crispr,scissors enzyme,base sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>진화론</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>자연선택,적응,종분화</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>evolution,natural selection,adaptation,speciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>호르몬</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>내분비,인슐린,항상성</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>hormone,endocrine,insulin,homeostasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>줄기세포</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>분화능,재생의학,배아</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>stem cell,differentiation potential,regenerative medicine,embryo</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>백신</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>항원주입,집단면역,접종</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>vaccine,antigen injection,herd immunity,inoculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>생물다양성</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>종풍부도,보전,생태계서비스</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>biodiversity,species richness,conservation,ecosystem services</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>기후변화</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>탄소중립,해수면상승,이상기후</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>climate change,carbon neutrality,sea level rise,abnormal weather</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>오존층</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>자외선차단,프레온가스,몬트리올</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ozone layer,uv shielding,freon gas,montreal</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>빙하기</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>간빙기,밀란코비치,해수면하강</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ice age,interglacial,milankovitch,sea level fall</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>암흑물질</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>중력렌즈,은하회전,보이지않는</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>dark matter,gravitational lens,galaxy rotation,invisible</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>중력파</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>시공간물결,라이고,병합관측</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>gravitational waves,spacetime ripples,ligo,merger observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>나노기술</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>원자단위,탄소나노튜브,신소재</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>nanotechnology,atomic scale,carbon nanotube,new material</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>미분</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>순간변화율,접선,도함수</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>differentiation,instantaneous rate of change,tangent,derivative</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>적분</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>넓이,원시함수,구분구적</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>integration,area,antiderivative,riemann sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>확률분포</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>정규곡선,표준편차,기댓값</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>probability distribution,normal curve,standard deviation,expected value</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>행렬</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>고유값,가우스소거,선형변환</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>matrix,eigenvalue,gaussian elimination,linear transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>소수</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>약수,에라토스테네스,암호이론</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>과학</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>prime number,divisor,eratosthenes,cryptography theory</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>게임이론</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>내쉬균형,죄수의딜레마,전략</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>game theory,nash equilibrium,prisoners dilemma,strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>인플레이션</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>통화량,구매력하락,기준금리</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>inflation,money supply,purchasing power decline,base rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>국내총생산</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>부가가치,경제성장률,국민계정</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>gross domestic product,value added,growth rate,national accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>통화정책</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>중앙은행,금리조정,양적완화</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>monetary policy,central bank,rate adjustment,quantitative easing</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>공공재</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>비배제성,무임승차,외부효과</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>public goods,non-excludability,free riding,externality</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>독점</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>진입장벽,가격결정력,공정거래</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>monopoly,entry barrier,pricing power,fair trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>자본주의</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>사유재산,이윤추구,자유경쟁</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>capitalism,private property,profit seeking,free competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>공리주의</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>최대다수,쾌락계산,벤담</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>utilitarianism,greatest number,hedonic calculus,bentham</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>정의론</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>무지의베일,롤스,공정성</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>theory of justice,veil of ignorance,rawls,fairness</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>실존주의</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>사르트르,자유의지,부조리</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>existentialism,sartre,free will,absurdity</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>구조주의</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>기호체계,레비스트로스,심층구조</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>structuralism,sign system,levi-strauss,deep structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>유럽연합</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>단일시장,유로화,브렉시트</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>사회</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>european union,single market,euro,brexit</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>냉전</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>철의장막,군비경쟁,양극체제</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>cold war,iron curtain,arms race,bipolar order</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>제국주의</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>식민지,원료공급지,열강</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>imperialism,colony,raw material source,great powers</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>산업화</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>도시집중,공장제,노동운동</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>industrialization,urban concentration,factory system,labor movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>종교개혁</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>루터,면죄부,신교</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>reformation,luther,indulgences,protestantism</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>계몽주의</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>이성,사회계약,백과전서</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>enlightenment,reason,social contract,encyclopedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>몽골제국</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>칭기즈칸,역참,유라시아</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>mongol empire,genghis khan,relay station,eurasia</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>실크로드</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>대상무역,교역로,오아시스도시</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>silk road,caravan trade,trade route,oasis city</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>고려시대</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>무신정권,팔만대장경,삼별초</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>goryeo,military regime,tripitaka koreana,sambyeolcho</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>갑오개혁</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>근대화,신분제폐지,개화파</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>gabo reform,modernization,abolition of class system,enlightenment faction</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>동학농민운동</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>전봉준,폐정개혁,척왜양이</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>역사</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>donghak peasant movement,jeon bong-jun,reform of abuses,anti-foreign</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>딥러닝</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>신경망,역전파,은닉층</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>deep learning,neural network,backpropagation,hidden layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>블록체인</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>분산원장,해시,채굴</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>blockchain,distributed ledger,hash,mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>컴파일러</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>구문분석,기계어,최적화</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>compiler,parsing,machine code,optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>운영체제</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>프로세스,메모리관리,스케줄링</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>operating system,process,memory management,scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>네트워크</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>라우터,패킷,대역폭</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>network,router,packet,bandwidth</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>자연어처리</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>형태소,임베딩,토큰화</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>natural language processing,morpheme,embedding,tokenization</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>컴퓨터비전</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>이미지인식,합성곱,객체탐지</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>computer vision,image recognition,convolution,object detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>양자컴퓨터</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>큐비트,얽힘,중첩상태</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>quantum computer,qubit,entanglement,superposition state</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>사이버보안</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>제로데이,침투시험,랜섬웨어</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>정보기술</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>cybersecurity,zero day,penetration test,ransomware</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>포스트모더니즘</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>해체,탈중심,패러디</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>postmodernism,deconstruction,decentering,parody</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>낭만주의</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>감성,자연예찬,개인주의</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>romanticism,emotion,nature worship,individualism</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>바로크</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>명암대비,화려한장식,카라바조</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>baroque,chiaroscuro,ornate decoration,caravaggio</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>입체주의</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>피카소,다시점,분해</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>cubism,picasso,multiple viewpoints,fragmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>추상표현주의</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>폴록,액션페인팅,색면</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>abstract expressionism,pollock,action painting,color field</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>팝아트</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>워홀,대중문화,실크스크린</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>pop art,warhol,popular culture,silkscreen</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>고딕건축</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>첨탑,스테인드글라스,공중버팀벽</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>gothic architecture,spire,stained glass,flying buttress</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>바우하우스</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>기능주의,그로피우스,산업디자인</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>bauhaus,functionalism,gropius,industrial design</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>교향곡</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>악장,소나타형식,베토벤</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>symphony,movement,sonata form,beethoven</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>재즈</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>즉흥연주,스윙,블루노트</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>jazz,improvisation,swing,blue note</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>오페라</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>아리아,서곡,레치타티보</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>opera,aria,overture,recitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>판타지문학</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>세계관,마법체계,톨킨</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>fantasy literature,worldview,magic system,tolkien</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>영화이론</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>몽타주,미장센,롱테이크</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>film theory,montage,mise-en-scene,long take</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>언어학</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>음운,통사,의미론</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>문화예술</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>linguistics,phonology,syntax,semantics</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>숙성육</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>드라이에이징,효소분해,풍미</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>aged meat,dry aging,enzymatic breakdown,flavor</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>마이야르반응</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>갈변,아미노산,환원당</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>maillard reaction,browning,amino acid,reducing sugar</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>저온조리</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>수비드,진공포장,항온</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>매우 어려움</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>음식</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>low-temperature cooking,sous vide,vacuum packing,constant temperature</t>
         </is>
       </c>
     </row>

--- a/교육용_대전게임_문제데이터_v2.xlsx
+++ b/교육용_대전게임_문제데이터_v2.xlsx
@@ -1689,7 +1689,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>theory of relativity,spacetime,gravity,speed of light</t>
+          <t>theory of relativity,spacetime,gravity,speed of light,아인슈타인,상대론,빛의속도</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>quantum mechanics,wave function,superposition,uncertainty</t>
+          <t>quantum mechanics,wave function,superposition,uncertainty,입자,불확실</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>genetics,allele,genotype,phenotype</t>
+          <t>genetics,allele,genotype,phenotype,멘델,우성열성</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>immune response,antibody,antigen,immune cell</t>
+          <t>immune response,antibody,antigen,immune cell,백신,림프구</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>neuroplasticity,synapse,learning,neural circuit</t>
+          <t>neuroplasticity,synapse,learning,neural circuit,뉴런</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>plate tectonics,subduction,mantle,plate boundary</t>
+          <t>plate tectonics,subduction,mantle,plate boundary,지각,대륙,지진</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>behavioral economics,loss aversion,heuristic,bias</t>
+          <t>behavioral economics,loss aversion,heuristic,bias,비합리,카너먼</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>social contract theory,state of nature,sovereignty,contract</t>
+          <t>social contract theory,state of nature,sovereignty,contract,홉스,루소</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>opportunity cost,marginal utility,choice,alternative</t>
+          <t>opportunity cost,marginal utility,choice,alternative,경제,희소성</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>globalization,value chain,trade,multinational corporation</t>
+          <t>globalization,value chain,trade,multinational corporation,국제,글로벌,국경</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Renaissance,humanism,perspective,classicism</t>
+          <t>Renaissance,humanism,perspective,classicism,문예부흥,레오나르도</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>industrial heritage,cultural regeneration,preservation,reuse</t>
+          <t>industrial heritage,cultural regeneration,preservation,reuse,폐공장</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>object-oriented programming,polymorphism,inheritance,encapsulation</t>
+          <t>object-oriented programming,polymorphism,inheritance,encapsulation,클래스</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>machine learning,overfitting,training data,validation</t>
+          <t>machine learning,overfitting,training data,validation,기계학습,인공지능,훈련</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>database,normalization,table,primary key</t>
+          <t>database,normalization,table,primary key,DB,관계형</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Impressionism,color division,Monet,plein air painting</t>
+          <t>Impressionism,color division,Monet,plein air painting,인상파,빛의화가</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>harmony,modulation,chord,interval</t>
+          <t>harmony,modulation,chord,interval,음악이론,코드진행</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>fermented food,lactic acid bacteria,microorganism,acidity</t>
+          <t>fermented food,lactic acid bacteria,microorganism,acidity,김치,효모</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>molecular gastronomy,spherification,alginate,texture</t>
+          <t>molecular gastronomy,spherification,alginate,texture,분자미식</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ethology,imprinting,instinct,social behavior</t>
+          <t>ethology,imprinting,instinct,social behavior,로렌츠</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>thermodynamics,entropy,heat engine,energy conservation</t>
+          <t>thermodynamics,entropy,heat engine,energy conservation,무질서</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>electromagnetic induction,faraday,flux change,induced current</t>
+          <t>electromagnetic induction,faraday,flux change,induced current,자기장</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>doppler effect,wavelength shift,redshift,ambulance sound</t>
+          <t>doppler effect,wavelength shift,redshift,ambulance sound,소리높낮이</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>black hole,event horizon,singularity,schwarzschild</t>
+          <t>black hole,event horizon,singularity,schwarzschild,중력붕괴,빛도탈출</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>big bang theory,cosmic expansion,background radiation,early universe</t>
+          <t>big bang theory,cosmic expansion,background radiation,early universe,대폭발,우주탄생</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>nuclear fusion,plasma,deuterium,tokamak</t>
+          <t>nuclear fusion,plasma,deuterium,tokamak,태양,핵반응</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>semiconductor,silicon,doping,transistor</t>
+          <t>semiconductor,silicon,doping,transistor,전도성</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>superconductor,critical temperature,zero resistance,meissner</t>
+          <t>superconductor,critical temperature,zero resistance,meissner,전기저항,극저온</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>chemical equilibrium,le chatelier,reverse reaction,equilibrium constant</t>
+          <t>chemical equilibrium,le chatelier,reverse reaction,equilibrium constant,화학반응</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>organic chemistry,hydrocarbon,functional group,isomer</t>
+          <t>organic chemistry,hydrocarbon,functional group,isomer,탄소화합물,탄소</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>enthalpy,heat of reaction,exothermic,endothermic</t>
+          <t>enthalpy,heat of reaction,exothermic,endothermic,열량,열출입</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>dna replication,double helix,polymerase,semiconservative</t>
+          <t>dna replication,double helix,polymerase,semiconservative,유전물질,디엔에이</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>protein synthesis,transcription,translation,ribosome</t>
+          <t>protein synthesis,transcription,translation,ribosome,유전정보</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>gene editing,crispr,scissors enzyme,base sequence</t>
+          <t>gene editing,crispr,scissors enzyme,base sequence,유전자가위,게놈</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>evolution,natural selection,adaptation,speciation</t>
+          <t>evolution,natural selection,adaptation,speciation,다윈,자연도태</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>hormone,endocrine,insulin,homeostasis</t>
+          <t>hormone,endocrine,insulin,homeostasis,혈당</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>vaccine,antigen injection,herd immunity,inoculation</t>
+          <t>vaccine,antigen injection,herd immunity,inoculation,항체</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>biodiversity,species richness,conservation,ecosystem services</t>
+          <t>biodiversity,species richness,conservation,ecosystem services,종다양성,생물종</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>climate change,carbon neutrality,sea level rise,abnormal weather</t>
+          <t>climate change,carbon neutrality,sea level rise,abnormal weather,온난화,지구온도</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>ice age,interglacial,milankovitch,sea level fall</t>
+          <t>ice age,interglacial,milankovitch,sea level fall,얼음</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>gravitational waves,spacetime ripples,ligo,merger observation</t>
+          <t>gravitational waves,spacetime ripples,ligo,merger observation,파동,아인슈타인</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>nanotechnology,atomic scale,carbon nanotube,new material</t>
+          <t>nanotechnology,atomic scale,carbon nanotube,new material,초미세,미세구조</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>differentiation,instantaneous rate of change,tangent,derivative</t>
+          <t>differentiation,instantaneous rate of change,tangent,derivative,미적분,기울기</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>integration,area,antiderivative,riemann sum</t>
+          <t>integration,area,antiderivative,riemann sum,면적,곡선아래</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>probability distribution,normal curve,standard deviation,expected value</t>
+          <t>probability distribution,normal curve,standard deviation,expected value,종모양</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>matrix,eigenvalue,gaussian elimination,linear transformation</t>
+          <t>matrix,eigenvalue,gaussian elimination,linear transformation,벡터,선형대수</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>prime number,divisor,eratosthenes,cryptography theory</t>
+          <t>prime number,divisor,eratosthenes,cryptography theory,나누어떨어지지</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>game theory,nash equilibrium,prisoners dilemma,strategy</t>
+          <t>game theory,nash equilibrium,prisoners dilemma,strategy,협력과배신</t>
         </is>
       </c>
     </row>
@@ -11079,7 +11079,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>inflation,money supply,purchasing power decline,base rate</t>
+          <t>inflation,money supply,purchasing power decline,base rate,물가,화폐</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>gross domestic product,value added,growth rate,national accounts</t>
+          <t>gross domestic product,value added,growth rate,national accounts,지디피</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>monetary policy,central bank,rate adjustment,quantitative easing</t>
+          <t>monetary policy,central bank,rate adjustment,quantitative easing,한국은행</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>public goods,non-excludability,free riding,externality</t>
+          <t>public goods,non-excludability,free riding,externality,시장실패</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>monopoly,entry barrier,pricing power,fair trade</t>
+          <t>monopoly,entry barrier,pricing power,fair trade,독과점,시장지배,기업</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>capitalism,private property,profit seeking,free competition</t>
+          <t>capitalism,private property,profit seeking,free competition,시장경제</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>utilitarianism,greatest number,hedonic calculus,bentham</t>
+          <t>utilitarianism,greatest number,hedonic calculus,bentham,행복</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>theory of justice,veil of ignorance,rawls,fairness</t>
+          <t>theory of justice,veil of ignorance,rawls,fairness,롤즈</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>structuralism,sign system,levi-strauss,deep structure</t>
+          <t>structuralism,sign system,levi-strauss,deep structure,언어구조</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>european union,single market,euro,brexit</t>
+          <t>european union,single market,euro,brexit,통화통합</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>cold war,iron curtain,arms race,bipolar order</t>
+          <t>cold war,iron curtain,arms race,bipolar order,소련,미국</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>imperialism,colony,raw material source,great powers</t>
+          <t>imperialism,colony,raw material source,great powers,침략</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>industrialization,urban concentration,factory system,labor movement</t>
+          <t>industrialization,urban concentration,factory system,labor movement,산업혁명,도시화</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>reformation,luther,indulgences,protestantism</t>
+          <t>reformation,luther,indulgences,protestantism,가톨릭</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>enlightenment,reason,social contract,encyclopedia</t>
+          <t>enlightenment,reason,social contract,encyclopedia,볼테르</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>silk road,caravan trade,trade route,oasis city</t>
+          <t>silk road,caravan trade,trade route,oasis city,비단길</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>deep learning,neural network,backpropagation,hidden layer</t>
+          <t>deep learning,neural network,backpropagation,hidden layer,인공지능</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>blockchain,distributed ledger,hash,mining</t>
+          <t>blockchain,distributed ledger,hash,mining,비트코인</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>compiler,parsing,machine code,optimization</t>
+          <t>compiler,parsing,machine code,optimization,번역,프로그래밍언어</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>operating system,process,memory management,scheduling</t>
+          <t>operating system,process,memory management,scheduling,윈도우,커널</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>network,router,packet,bandwidth</t>
+          <t>network,router,packet,bandwidth,인터넷,통신망</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>natural language processing,morpheme,embedding,tokenization</t>
+          <t>natural language processing,morpheme,embedding,tokenization,언어처리,말뭉치</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>computer vision,image recognition,convolution,object detection</t>
+          <t>computer vision,image recognition,convolution,object detection,영상인식,사진</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>cybersecurity,zero day,penetration test,ransomware</t>
+          <t>cybersecurity,zero day,penetration test,ransomware,해킹,악성코드</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>postmodernism,deconstruction,decentering,parody</t>
+          <t>postmodernism,deconstruction,decentering,parody,모던,탈근대</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>romanticism,emotion,nature worship,individualism</t>
+          <t>romanticism,emotion,nature worship,individualism,감정</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>baroque,chiaroscuro,ornate decoration,caravaggio</t>
+          <t>baroque,chiaroscuro,ornate decoration,caravaggio,극적,17세기</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>cubism,picasso,multiple viewpoints,fragmentation</t>
+          <t>cubism,picasso,multiple viewpoints,fragmentation,입체파,큐비즘</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>abstract expressionism,pollock,action painting,color field</t>
+          <t>abstract expressionism,pollock,action painting,color field,미국화가</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>pop art,warhol,popular culture,silkscreen</t>
+          <t>pop art,warhol,popular culture,silkscreen,대중예술</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>gothic architecture,spire,stained glass,flying buttress</t>
+          <t>gothic architecture,spire,stained glass,flying buttress,성당,중세건축</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>bauhaus,functionalism,gropius,industrial design</t>
+          <t>bauhaus,functionalism,gropius,industrial design,독일디자인</t>
         </is>
       </c>
     </row>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>symphony,movement,sonata form,beethoven</t>
+          <t>symphony,movement,sonata form,beethoven,심포니,교향악,오케스트라</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>jazz,improvisation,swing,blue note</t>
+          <t>jazz,improvisation,swing,blue note,흑인음악</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>opera,aria,overture,recitative</t>
+          <t>opera,aria,overture,recitative,성악,극장</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>fantasy literature,worldview,magic system,tolkien</t>
+          <t>fantasy literature,worldview,magic system,tolkien,환상소설</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>film theory,montage,mise-en-scene,long take</t>
+          <t>film theory,montage,mise-en-scene,long take,촬영기법</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>linguistics,phonology,syntax,semantics</t>
+          <t>linguistics,phonology,syntax,semantics,말소리,문법</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>aged meat,dry aging,enzymatic breakdown,flavor</t>
+          <t>aged meat,dry aging,enzymatic breakdown,flavor,고기,건조</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>maillard reaction,browning,amino acid,reducing sugar</t>
+          <t>maillard reaction,browning,amino acid,reducing sugar,갈색,굽기</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>low-temperature cooking,sous vide,vacuum packing,constant temperature</t>
+          <t>low-temperature cooking,sous vide,vacuum packing,constant temperature,조리법</t>
         </is>
       </c>
     </row>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>정말 쉬운 일상 주제. 필수어 3개 중 1개 이상 답변에 있으면 통과</t>
+          <t>정말 쉬운 일상 주제. 주제어와 필수어 3개(모두 4개) 중 1개 이상 답변에 있으면 통과</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>필수어 3개 중 1개 이상 답변에 있으면 통과</t>
+          <t>주제어와 필수어 3개(모두 4개) 중 1개 이상 답변에 있으면 통과</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>필수어 3개 중 2개 이상 답변에 있으면 통과</t>
+          <t>주제어와 필수어 3개(모두 4개) 중 2개 이상 답변에 있으면 통과</t>
         </is>
       </c>
     </row>
@@ -12700,11 +12700,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>필수어 3개 모두 답변에 있어야 통과</t>
+          <t>주제어와 필수어 3개, 모두 4개가 답변에 있어야 통과</t>
         </is>
       </c>
     </row>
